--- a/manpower_log/HC03.xlsx
+++ b/manpower_log/HC03.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\servadmin\Desktop\Saudi Ic\manpower_log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74BFA04-FAA5-406C-9A78-A328E2B6CD01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D791903E-8BFB-4774-ADCC-A4F2FE7FBCD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1236" yWindow="0" windowWidth="19920" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HC03" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HC03'!$D$1:$D$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HC03'!$D$1:$D$197</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="234">
   <si>
     <t>HC03</t>
   </si>
@@ -312,9 +312,6 @@
     <t>AMIR HAMJA MOLLA</t>
   </si>
   <si>
-    <t>ADAR BEPARY</t>
-  </si>
-  <si>
     <t>AL MAMUN</t>
   </si>
   <si>
@@ -540,9 +537,6 @@
     <t>Muhammad Shfeek</t>
   </si>
   <si>
-    <t>Surendra Nathu</t>
-  </si>
-  <si>
     <t>Banwari</t>
   </si>
   <si>
@@ -727,13 +721,28 @@
   </si>
   <si>
     <t>Surveyor</t>
+  </si>
+  <si>
+    <t>Md hanef molla</t>
+  </si>
+  <si>
+    <t>md lithon shaik</t>
+  </si>
+  <si>
+    <t>imdadul biswas</t>
+  </si>
+  <si>
+    <t>fariduzzaman</t>
+  </si>
+  <si>
+    <t>Jamaldduin Ansari</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -746,27 +755,27 @@
       <sz val="12"/>
       <color theme="0" tint="-4.9989318521683403E-2"/>
       <name val="Algerian"/>
-      <charset val="134"/>
+      <family val="5"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -774,24 +783,31 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -855,6 +871,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1029,7 +1051,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1108,6 +1130,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1461,12 +1486,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J194"/>
+  <dimension ref="A1:J197"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.77734375" customWidth="1"/>
     <col min="2" max="2" width="34.5546875" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.21875" customWidth="1"/>
     <col min="5" max="5" width="12.109375" customWidth="1"/>
     <col min="6" max="6" width="8.109375" customWidth="1"/>
@@ -1476,13 +1501,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -1546,7 +1571,7 @@
         <v>10</v>
       </c>
       <c r="H4" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
@@ -1631,7 +1656,7 @@
       </c>
       <c r="H8" s="4">
         <f>SUM(H2:H7)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>20</v>
@@ -1681,12 +1706,12 @@
         <v>10</v>
       </c>
       <c r="E11" s="7"/>
-      <c r="G11" s="28" t="s">
+      <c r="G11" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="31"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1">
       <c r="A12" s="7">
@@ -1731,13 +1756,13 @@
         <v>32</v>
       </c>
       <c r="H13" s="12">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I13" s="19">
         <v>35</v>
       </c>
       <c r="J13" s="19">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1">
@@ -1840,10 +1865,10 @@
         <v>41</v>
       </c>
       <c r="H17" s="12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I17" s="20">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J17" s="20">
         <v>0</v>
@@ -1977,10 +2002,10 @@
         <v>51</v>
       </c>
       <c r="H22" s="12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I22" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="20">
         <v>0</v>
@@ -2106,7 +2131,7 @@
       </c>
       <c r="H27" s="16">
         <f>SUM(H13:H26)</f>
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I27" s="21">
         <f>SUM(I13:I26)</f>
@@ -2114,7 +2139,7 @@
       </c>
       <c r="J27" s="21">
         <f>SUM(J13:J26)</f>
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1">
@@ -2584,7 +2609,7 @@
     </row>
     <row r="59" spans="1:5" ht="15" customHeight="1">
       <c r="A59" s="13">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>92</v>
@@ -2599,7 +2624,7 @@
     </row>
     <row r="60" spans="1:5" ht="15" customHeight="1">
       <c r="A60" s="13">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>93</v>
@@ -2614,7 +2639,7 @@
     </row>
     <row r="61" spans="1:5" ht="15" customHeight="1">
       <c r="A61" s="13">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>94</v>
@@ -2629,7 +2654,7 @@
     </row>
     <row r="62" spans="1:5" ht="15" customHeight="1">
       <c r="A62" s="13">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>95</v>
@@ -2644,7 +2669,7 @@
     </row>
     <row r="63" spans="1:5" ht="15" customHeight="1">
       <c r="A63" s="13">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>96</v>
@@ -2659,7 +2684,7 @@
     </row>
     <row r="64" spans="1:5" ht="15" customHeight="1">
       <c r="A64" s="13">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B64" s="14" t="s">
         <v>97</v>
@@ -2674,7 +2699,7 @@
     </row>
     <row r="65" spans="1:5" ht="15" customHeight="1">
       <c r="A65" s="13">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>98</v>
@@ -2689,7 +2714,7 @@
     </row>
     <row r="66" spans="1:5" ht="15" customHeight="1">
       <c r="A66" s="13">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>99</v>
@@ -2704,10 +2729,10 @@
     </row>
     <row r="67" spans="1:5" ht="15" customHeight="1">
       <c r="A67" s="13">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>100</v>
+        <v>229</v>
       </c>
       <c r="C67" s="18" t="s">
         <v>87</v>
@@ -2719,58 +2744,58 @@
     </row>
     <row r="68" spans="1:5" ht="15" customHeight="1">
       <c r="A68" s="13">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="C68" s="14">
-        <v>1917</v>
+        <v>230</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>87</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E68" s="14"/>
     </row>
     <row r="69" spans="1:5" ht="15" customHeight="1">
       <c r="A69" s="13">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="C69" s="14">
-        <v>2794</v>
+        <v>232</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>87</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E69" s="14"/>
     </row>
     <row r="70" spans="1:5" ht="15" customHeight="1">
       <c r="A70" s="13">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C70" s="14">
-        <v>4170</v>
+        <v>231</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>87</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E70" s="14"/>
     </row>
     <row r="71" spans="1:5" ht="15" customHeight="1">
       <c r="A71" s="13">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C71" s="14">
-        <v>4159</v>
+        <v>1917</v>
       </c>
       <c r="D71" s="14" t="s">
         <v>43</v>
@@ -2779,13 +2804,13 @@
     </row>
     <row r="72" spans="1:5" ht="15" customHeight="1">
       <c r="A72" s="13">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C72" s="14">
-        <v>4171</v>
+        <v>2794</v>
       </c>
       <c r="D72" s="14" t="s">
         <v>43</v>
@@ -2794,13 +2819,13 @@
     </row>
     <row r="73" spans="1:5" ht="15" customHeight="1">
       <c r="A73" s="13">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C73" s="14">
-        <v>4168</v>
+        <v>4170</v>
       </c>
       <c r="D73" s="14" t="s">
         <v>43</v>
@@ -2809,13 +2834,13 @@
     </row>
     <row r="74" spans="1:5" ht="15" customHeight="1">
       <c r="A74" s="13">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C74" s="14">
-        <v>4172</v>
+        <v>4159</v>
       </c>
       <c r="D74" s="14" t="s">
         <v>43</v>
@@ -2824,13 +2849,13 @@
     </row>
     <row r="75" spans="1:5" ht="15" customHeight="1">
       <c r="A75" s="13">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C75" s="14">
-        <v>4154</v>
+        <v>4171</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>43</v>
@@ -2839,13 +2864,13 @@
     </row>
     <row r="76" spans="1:5" ht="15" customHeight="1">
       <c r="A76" s="13">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C76" s="17">
-        <v>4204</v>
+        <v>105</v>
+      </c>
+      <c r="C76" s="14">
+        <v>4168</v>
       </c>
       <c r="D76" s="14" t="s">
         <v>43</v>
@@ -2854,13 +2879,13 @@
     </row>
     <row r="77" spans="1:5" ht="15" customHeight="1">
       <c r="A77" s="13">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C77" s="17">
-        <v>4555</v>
+        <v>106</v>
+      </c>
+      <c r="C77" s="14">
+        <v>4172</v>
       </c>
       <c r="D77" s="14" t="s">
         <v>43</v>
@@ -2869,13 +2894,13 @@
     </row>
     <row r="78" spans="1:5" ht="15" customHeight="1">
       <c r="A78" s="13">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C78" s="17">
-        <v>4556</v>
+        <v>107</v>
+      </c>
+      <c r="C78" s="14">
+        <v>4154</v>
       </c>
       <c r="D78" s="14" t="s">
         <v>43</v>
@@ -2884,13 +2909,13 @@
     </row>
     <row r="79" spans="1:5" ht="15" customHeight="1">
       <c r="A79" s="13">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C79" s="17">
-        <v>4560</v>
+        <v>4204</v>
       </c>
       <c r="D79" s="14" t="s">
         <v>43</v>
@@ -2899,13 +2924,13 @@
     </row>
     <row r="80" spans="1:5" ht="15" customHeight="1">
       <c r="A80" s="13">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C80" s="17">
-        <v>4563</v>
+        <v>4555</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>43</v>
@@ -2914,13 +2939,13 @@
     </row>
     <row r="81" spans="1:5" ht="15" customHeight="1">
       <c r="A81" s="13">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C81" s="17">
-        <v>4345</v>
+        <v>4556</v>
       </c>
       <c r="D81" s="14" t="s">
         <v>43</v>
@@ -2929,13 +2954,13 @@
     </row>
     <row r="82" spans="1:5" ht="15" customHeight="1">
       <c r="A82" s="13">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C82" s="17">
-        <v>2125</v>
+        <v>4560</v>
       </c>
       <c r="D82" s="14" t="s">
         <v>43</v>
@@ -2944,13 +2969,13 @@
     </row>
     <row r="83" spans="1:5" ht="15" customHeight="1">
       <c r="A83" s="13">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C83" s="17">
-        <v>4571</v>
+        <v>4563</v>
       </c>
       <c r="D83" s="14" t="s">
         <v>43</v>
@@ -2959,13 +2984,13 @@
     </row>
     <row r="84" spans="1:5" ht="15" customHeight="1">
       <c r="A84" s="13">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C84" s="17">
-        <v>4550</v>
+        <v>4345</v>
       </c>
       <c r="D84" s="14" t="s">
         <v>43</v>
@@ -2974,13 +2999,13 @@
     </row>
     <row r="85" spans="1:5" ht="15" customHeight="1">
       <c r="A85" s="13">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C85" s="17">
-        <v>4551</v>
+        <v>2125</v>
       </c>
       <c r="D85" s="14" t="s">
         <v>43</v>
@@ -2989,13 +3014,13 @@
     </row>
     <row r="86" spans="1:5" ht="15" customHeight="1">
       <c r="A86" s="13">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C86" s="17">
-        <v>4565</v>
+        <v>4571</v>
       </c>
       <c r="D86" s="14" t="s">
         <v>43</v>
@@ -3004,13 +3029,13 @@
     </row>
     <row r="87" spans="1:5" ht="15" customHeight="1">
       <c r="A87" s="13">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C87" s="17">
-        <v>2937</v>
+        <v>4550</v>
       </c>
       <c r="D87" s="14" t="s">
         <v>43</v>
@@ -3019,13 +3044,13 @@
     </row>
     <row r="88" spans="1:5" ht="15" customHeight="1">
       <c r="A88" s="13">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C88" s="17">
-        <v>4776</v>
+        <v>4551</v>
       </c>
       <c r="D88" s="14" t="s">
         <v>43</v>
@@ -3034,13 +3059,13 @@
     </row>
     <row r="89" spans="1:5" ht="15" customHeight="1">
       <c r="A89" s="13">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C89" s="17">
-        <v>4781</v>
+        <v>4565</v>
       </c>
       <c r="D89" s="14" t="s">
         <v>43</v>
@@ -3049,13 +3074,13 @@
     </row>
     <row r="90" spans="1:5" ht="15" customHeight="1">
       <c r="A90" s="13">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C90" s="17">
-        <v>4784</v>
+        <v>2937</v>
       </c>
       <c r="D90" s="14" t="s">
         <v>43</v>
@@ -3064,13 +3089,13 @@
     </row>
     <row r="91" spans="1:5" ht="15" customHeight="1">
       <c r="A91" s="13">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C91" s="17">
-        <v>4794</v>
+        <v>4776</v>
       </c>
       <c r="D91" s="14" t="s">
         <v>43</v>
@@ -3079,13 +3104,13 @@
     </row>
     <row r="92" spans="1:5" ht="15" customHeight="1">
       <c r="A92" s="13">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C92" s="17">
-        <v>2867</v>
+        <v>4781</v>
       </c>
       <c r="D92" s="14" t="s">
         <v>43</v>
@@ -3094,13 +3119,13 @@
     </row>
     <row r="93" spans="1:5" ht="15" customHeight="1">
       <c r="A93" s="13">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C93" s="17">
-        <v>2808</v>
+        <v>4784</v>
       </c>
       <c r="D93" s="14" t="s">
         <v>43</v>
@@ -3109,58 +3134,58 @@
     </row>
     <row r="94" spans="1:5" ht="15" customHeight="1">
       <c r="A94" s="13">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C94" s="17">
-        <v>2109</v>
+        <v>4794</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E94" s="14"/>
     </row>
     <row r="95" spans="1:5" ht="15" customHeight="1">
       <c r="A95" s="13">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C95" s="17">
-        <v>2002</v>
+        <v>2867</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E95" s="14"/>
     </row>
     <row r="96" spans="1:5" ht="15" customHeight="1">
       <c r="A96" s="13">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B96" s="14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C96" s="17">
-        <v>2996</v>
+        <v>2808</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E96" s="14"/>
     </row>
     <row r="97" spans="1:5" ht="15" customHeight="1">
       <c r="A97" s="13">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C97" s="17">
-        <v>3325</v>
+        <v>2109</v>
       </c>
       <c r="D97" s="14" t="s">
         <v>38</v>
@@ -3169,13 +3194,13 @@
     </row>
     <row r="98" spans="1:5" ht="15" customHeight="1">
       <c r="A98" s="13">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B98" s="14" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C98" s="17">
-        <v>2162</v>
+        <v>2002</v>
       </c>
       <c r="D98" s="14" t="s">
         <v>38</v>
@@ -3184,13 +3209,13 @@
     </row>
     <row r="99" spans="1:5" ht="15" customHeight="1">
       <c r="A99" s="13">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B99" s="14" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C99" s="17">
-        <v>2017</v>
+        <v>2996</v>
       </c>
       <c r="D99" s="14" t="s">
         <v>38</v>
@@ -3199,13 +3224,13 @@
     </row>
     <row r="100" spans="1:5" ht="15" customHeight="1">
       <c r="A100" s="13">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B100" s="14" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C100" s="17">
-        <v>2165</v>
+        <v>3325</v>
       </c>
       <c r="D100" s="14" t="s">
         <v>38</v>
@@ -3214,13 +3239,13 @@
     </row>
     <row r="101" spans="1:5" ht="15" customHeight="1">
       <c r="A101" s="13">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C101" s="17">
-        <v>1922</v>
+        <v>2162</v>
       </c>
       <c r="D101" s="14" t="s">
         <v>38</v>
@@ -3229,28 +3254,28 @@
     </row>
     <row r="102" spans="1:5" ht="15" customHeight="1">
       <c r="A102" s="13">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B102" s="14" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C102" s="17">
-        <v>1599</v>
-      </c>
-      <c r="D102" s="22" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D102" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E102" s="14"/>
     </row>
     <row r="103" spans="1:5" ht="15" customHeight="1">
       <c r="A103" s="13">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B103" s="14" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C103" s="17">
-        <v>2158</v>
+        <v>2165</v>
       </c>
       <c r="D103" s="14" t="s">
         <v>38</v>
@@ -3259,13 +3284,13 @@
     </row>
     <row r="104" spans="1:5" ht="15" customHeight="1">
       <c r="A104" s="13">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B104" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C104" s="17">
-        <v>4153</v>
+        <v>1922</v>
       </c>
       <c r="D104" s="14" t="s">
         <v>38</v>
@@ -3274,28 +3299,28 @@
     </row>
     <row r="105" spans="1:5" ht="15" customHeight="1">
       <c r="A105" s="13">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C105" s="17">
-        <v>4152</v>
-      </c>
-      <c r="D105" s="14" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D105" s="22" t="s">
         <v>38</v>
       </c>
       <c r="E105" s="14"/>
     </row>
     <row r="106" spans="1:5" ht="15" customHeight="1">
       <c r="A106" s="13">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B106" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C106" s="17">
-        <v>3067</v>
+        <v>2158</v>
       </c>
       <c r="D106" s="14" t="s">
         <v>38</v>
@@ -3304,13 +3329,13 @@
     </row>
     <row r="107" spans="1:5" ht="15" customHeight="1">
       <c r="A107" s="13">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B107" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C107" s="17">
-        <v>2738</v>
+        <v>4153</v>
       </c>
       <c r="D107" s="14" t="s">
         <v>38</v>
@@ -3319,256 +3344,256 @@
     </row>
     <row r="108" spans="1:5" ht="15" customHeight="1">
       <c r="A108" s="13">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C108" s="17">
-        <v>2814</v>
+        <v>4152</v>
       </c>
       <c r="D108" s="14" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="E108" s="14"/>
     </row>
     <row r="109" spans="1:5" ht="15" customHeight="1">
       <c r="A109" s="13">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B109" s="14" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C109" s="17">
-        <v>3163</v>
+        <v>3067</v>
       </c>
       <c r="D109" s="14" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="E109" s="14"/>
     </row>
     <row r="110" spans="1:5" ht="15" customHeight="1">
       <c r="A110" s="13">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C110" s="17">
-        <v>3196</v>
+        <v>2738</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="E110" s="14"/>
     </row>
     <row r="111" spans="1:5" ht="15" customHeight="1">
       <c r="A111" s="13">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C111" s="17">
-        <v>3198</v>
+        <v>2814</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E111" s="14"/>
     </row>
     <row r="112" spans="1:5" ht="15" customHeight="1">
       <c r="A112" s="13">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C112" s="17">
-        <v>3104</v>
+        <v>3163</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E112" s="14"/>
     </row>
     <row r="113" spans="1:5" ht="15" customHeight="1">
       <c r="A113" s="13">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C113" s="17">
-        <v>3555</v>
+        <v>3196</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E113" s="14"/>
     </row>
     <row r="114" spans="1:5" ht="15" customHeight="1">
       <c r="A114" s="13">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C114" s="17">
-        <v>3283</v>
+        <v>3198</v>
       </c>
       <c r="D114" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E114" s="14"/>
     </row>
     <row r="115" spans="1:5" ht="15" customHeight="1">
       <c r="A115" s="13">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B115" s="14" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C115" s="17">
-        <v>3281</v>
+        <v>3104</v>
       </c>
       <c r="D115" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E115" s="14"/>
     </row>
     <row r="116" spans="1:5" ht="15" customHeight="1">
       <c r="A116" s="13">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B116" s="14" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C116" s="17">
-        <v>3010</v>
+        <v>3555</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E116" s="14"/>
     </row>
     <row r="117" spans="1:5" ht="15" customHeight="1">
       <c r="A117" s="13">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B117" s="14" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C117" s="17">
-        <v>3234</v>
+        <v>3283</v>
       </c>
       <c r="D117" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E117" s="14"/>
     </row>
     <row r="118" spans="1:5" ht="15" customHeight="1">
       <c r="A118" s="13">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B118" s="14" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C118" s="17">
-        <v>4119</v>
+        <v>3281</v>
       </c>
       <c r="D118" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E118" s="14"/>
     </row>
     <row r="119" spans="1:5" ht="15" customHeight="1">
       <c r="A119" s="13">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B119" s="14" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C119" s="17">
-        <v>4130</v>
+        <v>3010</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E119" s="14"/>
     </row>
     <row r="120" spans="1:5" ht="15" customHeight="1">
       <c r="A120" s="13">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B120" s="14" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C120" s="17">
-        <v>4120</v>
+        <v>3234</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E120" s="14"/>
     </row>
     <row r="121" spans="1:5" ht="15" customHeight="1">
       <c r="A121" s="13">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B121" s="14" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C121" s="17">
-        <v>4136</v>
+        <v>4119</v>
       </c>
       <c r="D121" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E121" s="14"/>
     </row>
     <row r="122" spans="1:5" ht="15" customHeight="1">
       <c r="A122" s="13">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B122" s="14" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C122" s="17">
-        <v>4131</v>
+        <v>4130</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E122" s="14"/>
     </row>
     <row r="123" spans="1:5" ht="15" customHeight="1">
       <c r="A123" s="13">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B123" s="14" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C123" s="17">
-        <v>4123</v>
+        <v>4120</v>
       </c>
       <c r="D123" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E123" s="14"/>
     </row>
     <row r="124" spans="1:5" ht="15" customHeight="1">
       <c r="A124" s="13">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B124" s="14" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C124" s="17">
-        <v>2809</v>
+        <v>4136</v>
       </c>
       <c r="D124" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E124" s="14"/>
     </row>
@@ -3577,13 +3602,13 @@
         <v>109</v>
       </c>
       <c r="B125" s="14" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C125" s="17">
-        <v>2918</v>
+        <v>4131</v>
       </c>
       <c r="D125" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E125" s="14"/>
     </row>
@@ -3592,13 +3617,13 @@
         <v>110</v>
       </c>
       <c r="B126" s="14" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C126" s="17">
-        <v>2919</v>
+        <v>4123</v>
       </c>
       <c r="D126" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E126" s="14"/>
     </row>
@@ -3607,13 +3632,13 @@
         <v>111</v>
       </c>
       <c r="B127" s="14" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C127" s="17">
-        <v>2293</v>
+        <v>2809</v>
       </c>
       <c r="D127" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E127" s="14"/>
     </row>
@@ -3622,13 +3647,13 @@
         <v>112</v>
       </c>
       <c r="B128" s="14" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C128" s="17">
-        <v>2832</v>
+        <v>2918</v>
       </c>
       <c r="D128" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E128" s="14"/>
     </row>
@@ -3637,13 +3662,13 @@
         <v>113</v>
       </c>
       <c r="B129" s="14" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C129" s="17">
-        <v>2831</v>
+        <v>2919</v>
       </c>
       <c r="D129" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E129" s="14"/>
     </row>
@@ -3652,13 +3677,13 @@
         <v>114</v>
       </c>
       <c r="B130" s="14" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C130" s="17">
-        <v>2792</v>
+        <v>2293</v>
       </c>
       <c r="D130" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E130" s="14"/>
     </row>
@@ -3667,13 +3692,13 @@
         <v>115</v>
       </c>
       <c r="B131" s="14" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C131" s="17">
-        <v>2798</v>
+        <v>2832</v>
       </c>
       <c r="D131" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E131" s="14"/>
     </row>
@@ -3682,13 +3707,13 @@
         <v>116</v>
       </c>
       <c r="B132" s="14" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="C132" s="17">
-        <v>2791</v>
+        <v>2831</v>
       </c>
       <c r="D132" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E132" s="14"/>
     </row>
@@ -3697,73 +3722,73 @@
         <v>117</v>
       </c>
       <c r="B133" s="14" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C133" s="17">
-        <v>4472</v>
+        <v>2792</v>
       </c>
       <c r="D133" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E133" s="14"/>
     </row>
     <row r="134" spans="1:5" ht="15" customHeight="1">
       <c r="A134" s="13">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B134" s="14" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C134" s="17">
-        <v>4422</v>
+        <v>2798</v>
       </c>
       <c r="D134" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E134" s="14"/>
     </row>
     <row r="135" spans="1:5" ht="15" customHeight="1">
       <c r="A135" s="13">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B135" s="14" t="s">
-        <v>168</v>
+        <v>61</v>
       </c>
       <c r="C135" s="17">
-        <v>3012</v>
+        <v>2791</v>
       </c>
       <c r="D135" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E135" s="14"/>
     </row>
     <row r="136" spans="1:5" ht="15" customHeight="1">
       <c r="A136" s="13">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B136" s="14" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C136" s="17">
-        <v>4416</v>
+        <v>4472</v>
       </c>
       <c r="D136" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E136" s="14"/>
     </row>
     <row r="137" spans="1:5" ht="15" customHeight="1">
       <c r="A137" s="13">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B137" s="14" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C137" s="17">
-        <v>3197</v>
+        <v>4422</v>
       </c>
       <c r="D137" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E137" s="14"/>
     </row>
@@ -3772,13 +3797,13 @@
         <v>123</v>
       </c>
       <c r="B138" s="14" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C138" s="17">
-        <v>3068</v>
+        <v>4416</v>
       </c>
       <c r="D138" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E138" s="14"/>
     </row>
@@ -3787,13 +3812,13 @@
         <v>124</v>
       </c>
       <c r="B139" s="14" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C139" s="17">
-        <v>3838</v>
+        <v>3197</v>
       </c>
       <c r="D139" s="14" t="s">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="E139" s="14"/>
     </row>
@@ -3802,13 +3827,13 @@
         <v>125</v>
       </c>
       <c r="B140" s="14" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C140" s="17">
-        <v>4073</v>
+        <v>3068</v>
       </c>
       <c r="D140" s="14" t="s">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="E140" s="14"/>
     </row>
@@ -3817,10 +3842,10 @@
         <v>126</v>
       </c>
       <c r="B141" s="14" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C141" s="17">
-        <v>4072</v>
+        <v>3838</v>
       </c>
       <c r="D141" s="14" t="s">
         <v>36</v>
@@ -3832,10 +3857,10 @@
         <v>127</v>
       </c>
       <c r="B142" s="14" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C142" s="17">
-        <v>4080</v>
+        <v>4073</v>
       </c>
       <c r="D142" s="14" t="s">
         <v>36</v>
@@ -3847,10 +3872,10 @@
         <v>128</v>
       </c>
       <c r="B143" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="C143" s="14">
-        <v>4070</v>
+        <v>172</v>
+      </c>
+      <c r="C143" s="17">
+        <v>4072</v>
       </c>
       <c r="D143" s="14" t="s">
         <v>36</v>
@@ -3862,10 +3887,10 @@
         <v>129</v>
       </c>
       <c r="B144" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="C144" s="14">
-        <v>4065</v>
+        <v>173</v>
+      </c>
+      <c r="C144" s="17">
+        <v>4080</v>
       </c>
       <c r="D144" s="14" t="s">
         <v>36</v>
@@ -3877,10 +3902,10 @@
         <v>130</v>
       </c>
       <c r="B145" s="14" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C145" s="14">
-        <v>4212</v>
+        <v>4070</v>
       </c>
       <c r="D145" s="14" t="s">
         <v>36</v>
@@ -3892,10 +3917,10 @@
         <v>131</v>
       </c>
       <c r="B146" s="14" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C146" s="14">
-        <v>4071</v>
+        <v>4065</v>
       </c>
       <c r="D146" s="14" t="s">
         <v>36</v>
@@ -3907,10 +3932,10 @@
         <v>132</v>
       </c>
       <c r="B147" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C147" s="14">
-        <v>4703</v>
+        <v>4212</v>
       </c>
       <c r="D147" s="14" t="s">
         <v>36</v>
@@ -3922,10 +3947,10 @@
         <v>133</v>
       </c>
       <c r="B148" s="14" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C148" s="14">
-        <v>4066</v>
+        <v>4071</v>
       </c>
       <c r="D148" s="14" t="s">
         <v>36</v>
@@ -3937,10 +3962,10 @@
         <v>134</v>
       </c>
       <c r="B149" s="14" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C149" s="14">
-        <v>2962</v>
+        <v>4703</v>
       </c>
       <c r="D149" s="14" t="s">
         <v>36</v>
@@ -3951,26 +3976,26 @@
       <c r="A150" s="13">
         <v>135</v>
       </c>
-      <c r="B150" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="C150" s="7">
-        <v>2569</v>
-      </c>
-      <c r="D150" s="23" t="s">
+      <c r="B150" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="C150" s="14">
+        <v>4066</v>
+      </c>
+      <c r="D150" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E150" s="7"/>
+      <c r="E150" s="14"/>
     </row>
     <row r="151" spans="1:5" ht="15" customHeight="1">
       <c r="A151" s="13">
         <v>136</v>
       </c>
       <c r="B151" s="14" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C151" s="14">
-        <v>4067</v>
+        <v>2962</v>
       </c>
       <c r="D151" s="14" t="s">
         <v>36</v>
@@ -3981,26 +4006,26 @@
       <c r="A152" s="13">
         <v>137</v>
       </c>
-      <c r="B152" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="C152" s="14">
-        <v>4061</v>
-      </c>
-      <c r="D152" s="14" t="s">
+      <c r="B152" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C152" s="7">
+        <v>2569</v>
+      </c>
+      <c r="D152" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="E152" s="14"/>
+      <c r="E152" s="7"/>
     </row>
     <row r="153" spans="1:5" ht="15" customHeight="1">
       <c r="A153" s="13">
         <v>138</v>
       </c>
       <c r="B153" s="14" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C153" s="14">
-        <v>4081</v>
+        <v>4067</v>
       </c>
       <c r="D153" s="14" t="s">
         <v>36</v>
@@ -4012,10 +4037,10 @@
         <v>139</v>
       </c>
       <c r="B154" s="14" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C154" s="14">
-        <v>4075</v>
+        <v>4061</v>
       </c>
       <c r="D154" s="14" t="s">
         <v>36</v>
@@ -4027,10 +4052,10 @@
         <v>140</v>
       </c>
       <c r="B155" s="14" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C155" s="14">
-        <v>4082</v>
+        <v>4081</v>
       </c>
       <c r="D155" s="14" t="s">
         <v>36</v>
@@ -4042,10 +4067,10 @@
         <v>141</v>
       </c>
       <c r="B156" s="14" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C156" s="14">
-        <v>4063</v>
+        <v>4075</v>
       </c>
       <c r="D156" s="14" t="s">
         <v>36</v>
@@ -4057,10 +4082,10 @@
         <v>142</v>
       </c>
       <c r="B157" s="14" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C157" s="14">
-        <v>4496</v>
+        <v>4082</v>
       </c>
       <c r="D157" s="14" t="s">
         <v>36</v>
@@ -4072,10 +4097,10 @@
         <v>143</v>
       </c>
       <c r="B158" s="14" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C158" s="14">
-        <v>4537</v>
+        <v>4063</v>
       </c>
       <c r="D158" s="14" t="s">
         <v>36</v>
@@ -4087,10 +4112,10 @@
         <v>144</v>
       </c>
       <c r="B159" s="14" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C159" s="14">
-        <v>4062</v>
+        <v>4496</v>
       </c>
       <c r="D159" s="14" t="s">
         <v>36</v>
@@ -4102,10 +4127,10 @@
         <v>145</v>
       </c>
       <c r="B160" s="14" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C160" s="14">
-        <v>3043</v>
+        <v>4537</v>
       </c>
       <c r="D160" s="14" t="s">
         <v>36</v>
@@ -4117,10 +4142,10 @@
         <v>146</v>
       </c>
       <c r="B161" s="14" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C161" s="14">
-        <v>4495</v>
+        <v>4062</v>
       </c>
       <c r="D161" s="14" t="s">
         <v>36</v>
@@ -4132,10 +4157,10 @@
         <v>147</v>
       </c>
       <c r="B162" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="C162" s="22">
-        <v>33</v>
+        <v>191</v>
+      </c>
+      <c r="C162" s="14">
+        <v>3043</v>
       </c>
       <c r="D162" s="14" t="s">
         <v>36</v>
@@ -4147,10 +4172,10 @@
         <v>148</v>
       </c>
       <c r="B163" s="14" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C163" s="14">
-        <v>3276</v>
+        <v>4495</v>
       </c>
       <c r="D163" s="14" t="s">
         <v>36</v>
@@ -4162,10 +4187,10 @@
         <v>149</v>
       </c>
       <c r="B164" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="C164" s="14">
-        <v>2947</v>
+        <v>193</v>
+      </c>
+      <c r="C164" s="27">
+        <v>2604736492</v>
       </c>
       <c r="D164" s="14" t="s">
         <v>36</v>
@@ -4176,26 +4201,26 @@
       <c r="A165" s="13">
         <v>150</v>
       </c>
-      <c r="B165" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="C165" s="13">
-        <v>3277</v>
-      </c>
-      <c r="D165" s="13" t="s">
+      <c r="B165" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="C165" s="14">
+        <v>3276</v>
+      </c>
+      <c r="D165" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E165" s="13"/>
+      <c r="E165" s="14"/>
     </row>
     <row r="166" spans="1:5" ht="15" customHeight="1">
       <c r="A166" s="13">
         <v>151</v>
       </c>
       <c r="B166" s="14" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C166" s="14">
-        <v>4139</v>
+        <v>2947</v>
       </c>
       <c r="D166" s="14" t="s">
         <v>36</v>
@@ -4206,26 +4231,26 @@
       <c r="A167" s="13">
         <v>152</v>
       </c>
-      <c r="B167" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="C167" s="14">
-        <v>3679</v>
-      </c>
-      <c r="D167" s="14" t="s">
+      <c r="B167" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C167" s="13">
+        <v>3277</v>
+      </c>
+      <c r="D167" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E167" s="14"/>
+      <c r="E167" s="13"/>
     </row>
     <row r="168" spans="1:5" ht="15" customHeight="1">
       <c r="A168" s="13">
         <v>153</v>
       </c>
       <c r="B168" s="14" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C168" s="14">
-        <v>3388</v>
+        <v>4139</v>
       </c>
       <c r="D168" s="14" t="s">
         <v>36</v>
@@ -4237,10 +4262,10 @@
         <v>154</v>
       </c>
       <c r="B169" s="14" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C169" s="14">
-        <v>3003</v>
+        <v>3679</v>
       </c>
       <c r="D169" s="14" t="s">
         <v>36</v>
@@ -4252,10 +4277,10 @@
         <v>155</v>
       </c>
       <c r="B170" s="14" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C170" s="14">
-        <v>2978</v>
+        <v>3388</v>
       </c>
       <c r="D170" s="14" t="s">
         <v>36</v>
@@ -4267,10 +4292,10 @@
         <v>156</v>
       </c>
       <c r="B171" s="14" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C171" s="14">
-        <v>2601</v>
+        <v>3003</v>
       </c>
       <c r="D171" s="14" t="s">
         <v>36</v>
@@ -4282,10 +4307,10 @@
         <v>157</v>
       </c>
       <c r="B172" s="14" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C172" s="14">
-        <v>2223</v>
+        <v>2978</v>
       </c>
       <c r="D172" s="14" t="s">
         <v>36</v>
@@ -4297,10 +4322,10 @@
         <v>158</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C173" s="14">
-        <v>3677</v>
+        <v>2601</v>
       </c>
       <c r="D173" s="14" t="s">
         <v>36</v>
@@ -4312,10 +4337,10 @@
         <v>159</v>
       </c>
       <c r="B174" s="14" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C174" s="14">
-        <v>2817</v>
+        <v>2223</v>
       </c>
       <c r="D174" s="14" t="s">
         <v>36</v>
@@ -4327,10 +4352,10 @@
         <v>160</v>
       </c>
       <c r="B175" s="14" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C175" s="14">
-        <v>2820</v>
+        <v>3677</v>
       </c>
       <c r="D175" s="14" t="s">
         <v>36</v>
@@ -4342,10 +4367,10 @@
         <v>161</v>
       </c>
       <c r="B176" s="14" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C176" s="14">
-        <v>2080</v>
+        <v>2817</v>
       </c>
       <c r="D176" s="14" t="s">
         <v>36</v>
@@ -4357,10 +4382,10 @@
         <v>162</v>
       </c>
       <c r="B177" s="14" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C177" s="14">
-        <v>3390</v>
+        <v>2820</v>
       </c>
       <c r="D177" s="14" t="s">
         <v>36</v>
@@ -4372,10 +4397,10 @@
         <v>163</v>
       </c>
       <c r="B178" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="C178" s="22" t="s">
-        <v>212</v>
+        <v>207</v>
+      </c>
+      <c r="C178" s="14">
+        <v>2080</v>
       </c>
       <c r="D178" s="14" t="s">
         <v>36</v>
@@ -4387,10 +4412,10 @@
         <v>164</v>
       </c>
       <c r="B179" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="C179" s="22" t="s">
-        <v>212</v>
+        <v>208</v>
+      </c>
+      <c r="C179" s="14">
+        <v>3390</v>
       </c>
       <c r="D179" s="14" t="s">
         <v>36</v>
@@ -4402,10 +4427,10 @@
         <v>165</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C180" s="22" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D180" s="14" t="s">
         <v>36</v>
@@ -4417,13 +4442,13 @@
         <v>166</v>
       </c>
       <c r="B181" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="C181" s="14">
-        <v>1957</v>
+        <v>211</v>
+      </c>
+      <c r="C181" s="22" t="s">
+        <v>210</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>216</v>
+        <v>36</v>
       </c>
       <c r="E181" s="14"/>
     </row>
@@ -4432,13 +4457,13 @@
         <v>167</v>
       </c>
       <c r="B182" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="C182" s="24">
-        <v>2208</v>
+        <v>212</v>
+      </c>
+      <c r="C182" s="22" t="s">
+        <v>210</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>216</v>
+        <v>36</v>
       </c>
       <c r="E182" s="14"/>
     </row>
@@ -4447,199 +4472,242 @@
         <v>168</v>
       </c>
       <c r="B183" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="C183" s="25">
-        <v>2143</v>
+        <v>213</v>
+      </c>
+      <c r="C183" s="14">
+        <v>1957</v>
       </c>
       <c r="D183" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E183" s="14"/>
     </row>
     <row r="184" spans="1:10" ht="15" customHeight="1">
-      <c r="A184" s="13">
-        <v>169</v>
-      </c>
-      <c r="B184" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="C184" s="26">
-        <v>2147</v>
-      </c>
-      <c r="D184" s="26" t="s">
-        <v>216</v>
+      <c r="A184" s="13"/>
+      <c r="B184" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="C184" s="14">
+        <v>2097</v>
+      </c>
+      <c r="D184" s="14" t="s">
+        <v>214</v>
       </c>
       <c r="E184" s="14"/>
     </row>
     <row r="185" spans="1:10" ht="15" customHeight="1">
       <c r="A185" s="13">
-        <v>170</v>
-      </c>
-      <c r="B185" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="C185" s="26">
-        <v>1926</v>
-      </c>
-      <c r="D185" s="26" t="s">
-        <v>216</v>
+        <v>169</v>
+      </c>
+      <c r="B185" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="C185" s="24">
+        <v>2208</v>
+      </c>
+      <c r="D185" s="14" t="s">
+        <v>214</v>
       </c>
       <c r="E185" s="14"/>
     </row>
     <row r="186" spans="1:10" ht="15" customHeight="1">
       <c r="A186" s="13">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B186" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="C186" s="14">
-        <v>2965</v>
+        <v>216</v>
+      </c>
+      <c r="C186" s="25">
+        <v>2143</v>
       </c>
       <c r="D186" s="14" t="s">
-        <v>47</v>
+        <v>214</v>
       </c>
       <c r="E186" s="14"/>
     </row>
     <row r="187" spans="1:10" ht="15" customHeight="1">
       <c r="A187" s="13">
-        <v>172</v>
-      </c>
-      <c r="B187" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="C187" s="14">
-        <v>3239</v>
-      </c>
-      <c r="D187" s="14" t="s">
-        <v>53</v>
+        <v>171</v>
+      </c>
+      <c r="B187" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="C187" s="26">
+        <v>2147</v>
+      </c>
+      <c r="D187" s="26" t="s">
+        <v>214</v>
       </c>
       <c r="E187" s="14"/>
     </row>
     <row r="188" spans="1:10" ht="15" customHeight="1">
       <c r="A188" s="13">
-        <v>173</v>
-      </c>
-      <c r="B188" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="C188" s="14">
-        <v>2833</v>
-      </c>
-      <c r="D188" s="14" t="s">
-        <v>45</v>
+        <v>172</v>
+      </c>
+      <c r="B188" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C188" s="26">
+        <v>1926</v>
+      </c>
+      <c r="D188" s="26" t="s">
+        <v>214</v>
       </c>
       <c r="E188" s="14"/>
-      <c r="I188"/>
-      <c r="J188"/>
     </row>
     <row r="189" spans="1:10" ht="15" customHeight="1">
       <c r="A189" s="13">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B189" s="14" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C189" s="14">
-        <v>3066</v>
+        <v>2965</v>
       </c>
       <c r="D189" s="14" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E189" s="14"/>
     </row>
     <row r="190" spans="1:10" ht="15" customHeight="1">
       <c r="A190" s="13">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B190" s="14" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C190" s="14">
-        <v>3265</v>
+        <v>3239</v>
       </c>
       <c r="D190" s="14" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E190" s="14"/>
     </row>
     <row r="191" spans="1:10" ht="15" customHeight="1">
       <c r="A191" s="13">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B191" s="14" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C191" s="14">
-        <v>3048</v>
+        <v>2833</v>
       </c>
       <c r="D191" s="14" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E191" s="14"/>
+      <c r="I191"/>
+      <c r="J191"/>
     </row>
     <row r="192" spans="1:10" ht="15" customHeight="1">
       <c r="A192" s="13">
-        <v>177</v>
-      </c>
-      <c r="B192" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="C192" s="26">
-        <v>4401</v>
-      </c>
-      <c r="D192" s="26" t="s">
-        <v>55</v>
+        <v>176</v>
+      </c>
+      <c r="B192" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="C192" s="14">
+        <v>3066</v>
+      </c>
+      <c r="D192" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="E192" s="14"/>
     </row>
     <row r="193" spans="1:5" ht="15" customHeight="1">
       <c r="A193" s="13">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B193" s="14" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C193" s="14">
-        <v>3491</v>
+        <v>3265</v>
       </c>
       <c r="D193" s="14" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E193" s="14"/>
     </row>
     <row r="194" spans="1:5" ht="15" customHeight="1">
       <c r="A194" s="13">
+        <v>178</v>
+      </c>
+      <c r="B194" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="C194" s="14">
+        <v>3048</v>
+      </c>
+      <c r="D194" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E194" s="14"/>
+    </row>
+    <row r="195" spans="1:5" ht="15" customHeight="1">
+      <c r="A195" s="13">
         <v>179</v>
       </c>
-      <c r="B194" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="C194" s="14">
+      <c r="B195" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="C195" s="26">
+        <v>4401</v>
+      </c>
+      <c r="D195" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E195" s="14"/>
+    </row>
+    <row r="196" spans="1:5" ht="15" customHeight="1">
+      <c r="A196" s="13">
+        <v>180</v>
+      </c>
+      <c r="B196" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C196" s="14">
+        <v>3491</v>
+      </c>
+      <c r="D196" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E196" s="14"/>
+    </row>
+    <row r="197" spans="1:5" ht="15" customHeight="1">
+      <c r="A197" s="13">
+        <v>181</v>
+      </c>
+      <c r="B197" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C197" s="14">
         <v>2546</v>
       </c>
-      <c r="D194" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="E194" s="14"/>
+      <c r="D197" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="E197" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G11:J11"/>
   </mergeCells>
-  <conditionalFormatting sqref="C143">
+  <conditionalFormatting sqref="C145">
     <cfRule type="expression" dxfId="3" priority="9">
-      <formula>$A151</formula>
+      <formula>$A153</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="10">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C153:C154">
+  <conditionalFormatting sqref="C155:C156">
     <cfRule type="expression" dxfId="1" priority="6">
-      <formula>$A155</formula>
+      <formula>$A157</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="8">
       <formula>#REF!</formula>
